--- a/მომსახურების ანაზღაურება ცელერისი.xlsx
+++ b/მომსახურების ანაზღაურება ცელერისი.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F25BE-BB36-4336-A9D2-74423B39F50C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03124906-417B-421B-B968-37A48BB51EA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="97">
   <si>
     <t>8</t>
   </si>
@@ -439,16 +439,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -764,54 +760,54 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
-        <v>62003016407</v>
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A2,ინფო!A:A,0))</f>
-        <v>დავით</v>
+        <v>გიორგი</v>
       </c>
       <c r="C2" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A2,ინფო!A:A,0))</f>
-        <v>სვირავა</v>
+        <v>მელაძე</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="e">
         <f>INDEX(თანხები!D:D,MATCH(A2,თანხები!A:A,0))</f>
-        <v>3740.44</v>
+        <v>#N/A</v>
       </c>
       <c r="F2" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A2,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3">
-        <v>47001040600</v>
+      <c r="A3" t="s">
+        <v>32</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A3,ინფო!A:A,0))</f>
-        <v>რობერტ</v>
+        <v>დავითი</v>
       </c>
       <c r="C3" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A3,ინფო!A:A,0))</f>
-        <v>ელოიძე</v>
+        <v>საყვარელიძე</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E3">
         <f>INDEX(თანხები!D:D,MATCH(A3,თანხები!A:A,0))</f>
-        <v>1368.47</v>
+        <v>2573.61</v>
       </c>
       <c r="F3" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A3,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>1</v>
@@ -819,80 +815,77 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B4" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A4,ინფო!A:A,0))</f>
-        <v>დავითი</v>
+        <v>ბადრი</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A4,ინფო!A:A,0))</f>
-        <v>საყვარელიძე</v>
+        <v>სირაძე</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E4">
         <f>INDEX(თანხები!D:D,MATCH(A4,თანხები!A:A,0))</f>
-        <v>1326</v>
+        <v>2904.64</v>
       </c>
       <c r="F4" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A4,ინფო!A:A,0))</f>
-        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
+        <v>თბილისი გარდაბნის გზატ. N 42</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>24</v>
+      <c r="A5">
+        <v>62003016407</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A5,ინფო!A:A,0))</f>
-        <v>გიორგი</v>
+        <v>დავით</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A5,ინფო!A:A,0))</f>
-        <v>მელაძე</v>
+        <v>სვირავა</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="e">
         <f>INDEX(თანხები!D:D,MATCH(A5,თანხები!A:A,0))</f>
-        <v>1267.17</v>
+        <v>#N/A</v>
       </c>
       <c r="F5" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A5,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
+        <v>თბილისი</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="8" t="str">
+      <c r="B6" s="8" t="e">
         <f>INDEX(ინფო!B:B,MATCH(A6,ინფო!A:A,0))</f>
-        <v>ბადრი</v>
-      </c>
-      <c r="C6" s="8" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="8" t="e">
         <f>INDEX(ინფო!C:C,MATCH(A6,ინფო!A:A,0))</f>
-        <v>სირაძე</v>
+        <v>#N/A</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="e">
         <f>INDEX(თანხები!D:D,MATCH(A6,თანხები!A:A,0))</f>
-        <v>1114</v>
-      </c>
-      <c r="F6" s="5" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="F6" s="5" t="e">
         <f>INDEX(ინფო!D:D,MATCH(A6,ინფო!A:A,0))</f>
-        <v>თბილისი გარდაბნის გზატ. N 42</v>
+        <v>#N/A</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>1</v>
@@ -1472,7 +1465,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="16">
+      <c r="A20" s="14">
         <v>24001050126</v>
       </c>
       <c r="B20" t="s">
@@ -1577,17 +1570,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7E4943-2DCB-430A-830C-82E1F3476269}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.21875" style="6" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
         <v>43</v>
       </c>
@@ -1597,96 +1590,98 @@
       <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+    <row r="2" spans="1:7">
+      <c r="A2" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C2,ინფო!C:C,0))</f>
-        <v>62003016407</v>
+        <v>22001020425</v>
       </c>
       <c r="B2" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C2,ინფო!C:C,0))</f>
-        <v>დავით</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="18">
-        <v>3740.44</v>
-      </c>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+        <v>ბადრი</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="17">
+        <v>2904.64</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C3,ინფო!C:C,0))</f>
-        <v>47001040600</v>
+        <v>38001048993</v>
       </c>
       <c r="B3" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C3,ინფო!C:C,0))</f>
-        <v>რობერტ</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="18">
-        <v>1368.47</v>
-      </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5">
+        <v>დავითი</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="17">
+        <v>2573.61</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C4,ინფო!C:C,0))</f>
-        <v>38001048993</v>
+        <v>01010000461</v>
       </c>
       <c r="B4" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C4,ინფო!C:C,0))</f>
-        <v>დავითი</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="18">
-        <v>1326</v>
-      </c>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="str">
+        <v>მიხეილ</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17">
+        <v>1240.08</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C5,ინფო!C:C,0))</f>
-        <v>01030053229</v>
-      </c>
-      <c r="B5" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B5" t="e">
         <f>INDEX(ინფო!B:B,MATCH(C5,ინფო!C:C,0))</f>
-        <v>გიორგი</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="18">
-        <v>1267.17</v>
-      </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C6,ინფო!C:C,0))</f>
-        <v>22001020425</v>
-      </c>
-      <c r="B6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="B6" t="e">
         <f>INDEX(ინფო!B:B,MATCH(C6,ინფო!C:C,0))</f>
-        <v>ბადრი</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="18">
-        <v>1114</v>
-      </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C7,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1695,9 +1690,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C7,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C8,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1706,9 +1705,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C8,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C9,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1717,9 +1720,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C9,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C10,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1728,9 +1735,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C10,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C11,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1739,9 +1750,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C11,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="D11"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C12,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1750,10 +1765,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C12,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="C12" s="19"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C13,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1762,8 +1780,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C13,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="C13" s="17"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C14,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1772,8 +1795,13 @@
         <f>INDEX(ინფო!B:B,MATCH(C14,ინფო!C:C,0))</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" s="17"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C15,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1783,7 +1811,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:7">
       <c r="A16" t="e">
         <f>INDEX(ინფო!A:A,MATCH(C16,ინფო!C:C,0))</f>
         <v>#N/A</v>
@@ -1844,87 +1872,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D28A8-2A04-4213-9FF0-5FC7E21D8E88}">
-  <dimension ref="A2:M11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.77734375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13">
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="14"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="15"/>
-      <c r="C6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="18">
-        <v>3740.44</v>
-      </c>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="C7" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="18">
-        <v>1368.47</v>
-      </c>
-      <c r="M7" s="17"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="15"/>
-      <c r="C8" s="18" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1"/>
+      <c r="B1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2"/>
+      <c r="B2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3"/>
+      <c r="B3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4"/>
+      <c r="B4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5"/>
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2904.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6"/>
+      <c r="B6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="18">
-        <v>1326</v>
-      </c>
-      <c r="M8" s="17"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="15"/>
-      <c r="C9" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="18">
-        <v>1267.17</v>
-      </c>
-      <c r="M9" s="17"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="15"/>
-      <c r="C10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="18">
-        <v>1114</v>
-      </c>
-      <c r="M10" s="17"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="15"/>
-      <c r="C11" s="18"/>
-      <c r="M11" s="17"/>
+      <c r="C6" s="16">
+        <v>2573.61</v>
+      </c>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7"/>
+      <c r="B7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="16">
+        <v>1240.08</v>
+      </c>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12"/>
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13"/>
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14"/>
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15"/>
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16"/>
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17"/>
+      <c r="B17"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18"/>
+      <c r="B18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
